--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2311-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2311-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81B1CEFD-9F84-41BF-8517-F5513AB1F6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B86B44A-150A-4009-8AC0-81D5B5423875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{EC8F6A16-DF24-410B-A275-D73C2C8D51E1}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{5C3A2F7C-040B-4421-8039-4B588C71D7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="2311-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1258,19 +1258,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D45AEA-0EEB-4CBE-A125-6C593D68CF8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB0DFDB-B2D3-46A2-9178-1842AC51DA99}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" customWidth="1"/>
+    <col min="1" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1299,7 @@
       <c r="P1" s="18"/>
       <c r="Q1" s="19"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="15"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1352,7 +1350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="16"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1389,7 +1387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2023</v>
       </c>
@@ -1442,7 +1440,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="9">
         <v>2022</v>
       </c>
@@ -1495,7 +1493,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2021</v>
       </c>
@@ -1548,7 +1546,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="9">
         <v>2020</v>
       </c>
@@ -1601,7 +1599,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2019</v>
       </c>
@@ -1654,7 +1652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="9">
         <v>2018</v>
       </c>
@@ -1707,7 +1705,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2017</v>
       </c>
@@ -1760,7 +1758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="9">
         <v>2016</v>
       </c>
@@ -1813,7 +1811,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2015</v>
       </c>
@@ -1866,7 +1864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="9">
         <v>2014</v>
       </c>
@@ -1919,7 +1917,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2013</v>
       </c>
@@ -1972,7 +1970,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="9">
         <v>2012</v>
       </c>
@@ -2025,7 +2023,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2011</v>
       </c>
@@ -2078,7 +2076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="9">
         <v>2010</v>
       </c>
@@ -2131,7 +2129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2009</v>
       </c>
@@ -2184,7 +2182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="9">
         <v>2008</v>
       </c>
@@ -2237,7 +2235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2007</v>
       </c>
@@ -2290,7 +2288,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="9">
         <v>2006</v>
       </c>
@@ -2343,7 +2341,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2005</v>
       </c>
@@ -2396,7 +2394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="9">
         <v>2004</v>
       </c>
@@ -2449,7 +2447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2003</v>
       </c>
@@ -2502,7 +2500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="9">
         <v>2002</v>
       </c>
@@ -2555,7 +2553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2001</v>
       </c>
@@ -2608,7 +2606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="9">
         <v>2000</v>
       </c>
@@ -2661,7 +2659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>1999</v>
       </c>
@@ -2714,7 +2712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="9">
         <v>1998</v>
       </c>
@@ -2767,7 +2765,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1997</v>
       </c>
@@ -2820,7 +2818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="9">
         <v>1996</v>
       </c>
@@ -2873,7 +2871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1995</v>
       </c>
@@ -2926,7 +2924,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A33" s="9">
         <v>1994</v>
       </c>
@@ -2979,7 +2977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A34" s="6">
         <v>1993</v>
       </c>
@@ -3032,7 +3030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A35" s="9">
         <v>1992</v>
       </c>
@@ -3085,7 +3083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A36" s="6">
         <v>1991</v>
       </c>
@@ -3138,7 +3136,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A37" s="9">
         <v>1990</v>
       </c>
